--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-17 11:00:00</t>
+          <t>2026-09-17 10:15:00</t>
         </is>
       </c>
     </row>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,68 +1283,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-17 15:45:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-17 21:00:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,158 +3196,5048 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hapoel Afula</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hapoel Kfar Shalem</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Israel Liga Leumit</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Maccabi Kabilio Jaffa</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Maccabi Bnei Raina</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Olimpiyets</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Leningradets</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Torpedo Moskva</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Veles</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Norway Toppserien</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Trondheims-Ørn</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stabæk Women</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Norway Toppserien</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Vålerenga Women</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Haugesund W</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Estonia Meistriliiga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Tallinna FC Levadia</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tammeka</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>1.23</v>
+      </c>
+      <c r="O24">
+        <v>5.8</v>
+      </c>
+      <c r="P24">
+        <v>9.75</v>
+      </c>
+      <c r="Q24">
+        <v>2.33</v>
+      </c>
+      <c r="R24">
+        <v>2.85</v>
+      </c>
+      <c r="S24">
+        <v>1.2</v>
+      </c>
+      <c r="T24">
+        <v>3.7</v>
+      </c>
+      <c r="U24">
+        <v>1.56</v>
+      </c>
+      <c r="V24">
+        <v>2.1</v>
+      </c>
+      <c r="W24">
+        <v>1.16</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>1.09</v>
+      </c>
+      <c r="Z24">
+        <v>5.4</v>
+      </c>
+      <c r="AA24">
+        <v>1.16</v>
+      </c>
+      <c r="AB24">
+        <v>2.75</v>
+      </c>
+      <c r="AC24">
+        <v>1.45</v>
+      </c>
+      <c r="AD24">
+        <v>2.43</v>
+      </c>
+      <c r="AE24">
+        <v>1.65</v>
+      </c>
+      <c r="AF24">
+        <v>1.91</v>
+      </c>
+      <c r="AG24">
+        <v>1.76</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.15</v>
+      </c>
+      <c r="AK24">
+        <v>1.62</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Doqarah</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pro Vercelli</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Alcione</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AlbinoLeffe</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Arzignano Valchiampo</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Desenzano Calvina</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lecco</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Pergolettese</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Folgore Caratese</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Lumezzane</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Novara</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Cittadella</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Juventus II</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>US Biskra</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CR Belouizdad</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Getafe CF</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Durban City</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Russia Russian Premier League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Makhachkala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CSKA Moskva</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-09-17 14:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Serbia SuperLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Železničar Pančevo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>11.2</v>
+      </c>
+      <c r="O36">
+        <v>5.25</v>
+      </c>
+      <c r="P36">
+        <v>1.22</v>
+      </c>
+      <c r="Q36">
+        <v>8</v>
+      </c>
+      <c r="R36">
+        <v>2.88</v>
+      </c>
+      <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>4</v>
+      </c>
+      <c r="U36">
+        <v>2.13</v>
+      </c>
+      <c r="V36">
+        <v>1.7</v>
+      </c>
+      <c r="W36">
+        <v>1.18</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.1</v>
+      </c>
+      <c r="Z36">
+        <v>5.15</v>
+      </c>
+      <c r="AA36">
+        <v>1.53</v>
+      </c>
+      <c r="AB36">
+        <v>2.4</v>
+      </c>
+      <c r="AC36">
+        <v>2.3</v>
+      </c>
+      <c r="AD36">
+        <v>1.71</v>
+      </c>
+      <c r="AE36">
+        <v>1.22</v>
+      </c>
+      <c r="AF36">
+        <v>1.85</v>
+      </c>
+      <c r="AG36">
+        <v>1.67</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>4.2</v>
+      </c>
+      <c r="AK36">
+        <v>1.04</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>France National</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Bastia</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cannes</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-09-17 15:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Temouchent</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>England EFL League One</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Athletic Carpi</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ospitaletto</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>-1</v>
+      </c>
+      <c r="AN40">
+        <v>-1</v>
+      </c>
+      <c r="AO40">
+        <v>-1</v>
+      </c>
+      <c r="AP40">
+        <v>-1</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Giana Erminio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Trento</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>-1</v>
+      </c>
+      <c r="AN41">
+        <v>-1</v>
+      </c>
+      <c r="AO41">
+        <v>-1</v>
+      </c>
+      <c r="AP41">
+        <v>-1</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Renate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dolomiti Bellunesi</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>0</v>
+      </c>
+      <c r="AG42">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>0</v>
+      </c>
+      <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>-1</v>
+      </c>
+      <c r="AN42">
+        <v>-1</v>
+      </c>
+      <c r="AO42">
+        <v>-1</v>
+      </c>
+      <c r="AP42">
+        <v>-1</v>
+      </c>
+      <c r="AQ42">
+        <v>0</v>
+      </c>
+      <c r="AR42">
+        <v>0</v>
+      </c>
+      <c r="AS42">
+        <v>0</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Union Brescia</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Treviso</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>0</v>
+      </c>
+      <c r="AG43">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>0</v>
+      </c>
+      <c r="AK43">
+        <v>0</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>-1</v>
+      </c>
+      <c r="AN43">
+        <v>-1</v>
+      </c>
+      <c r="AO43">
+        <v>-1</v>
+      </c>
+      <c r="AP43">
+        <v>-1</v>
+      </c>
+      <c r="AQ43">
+        <v>0</v>
+      </c>
+      <c r="AR43">
+        <v>0</v>
+      </c>
+      <c r="AS43">
+        <v>0</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Málaga CF</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>0</v>
+      </c>
+      <c r="AG44">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>0</v>
+      </c>
+      <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>-1</v>
+      </c>
+      <c r="AN44">
+        <v>-1</v>
+      </c>
+      <c r="AO44">
+        <v>-1</v>
+      </c>
+      <c r="AP44">
+        <v>-1</v>
+      </c>
+      <c r="AQ44">
+        <v>0</v>
+      </c>
+      <c r="AR44">
+        <v>0</v>
+      </c>
+      <c r="AS44">
+        <v>0</v>
+      </c>
+      <c r="AT44">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-09-17 16:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>-1</v>
+      </c>
+      <c r="AN45">
+        <v>-1</v>
+      </c>
+      <c r="AO45">
+        <v>-1</v>
+      </c>
+      <c r="AP45">
+        <v>-1</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-09-17 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Croatia Druga HNL</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Kustošija</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Croatia Zmijavci</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>Mladost Ždralovi</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Segesta Sisak</t>
         </is>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
-      <c r="V18">
-        <v>0</v>
-      </c>
-      <c r="W18">
-        <v>0</v>
-      </c>
-      <c r="X18">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0</v>
-      </c>
-      <c r="AC18">
-        <v>0</v>
-      </c>
-      <c r="AD18">
-        <v>0</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>0</v>
-      </c>
-      <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>0</v>
-      </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>-1</v>
-      </c>
-      <c r="AN18">
-        <v>-1</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>-1</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>2026-09-17 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gualberto Villarroel SJ</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU48"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G5">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G6">
@@ -1283,68 +1283,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1408,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-17 12:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-09-17 13:00:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,68 +4217,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00:00</t>
+          <t>2026-09-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00:00</t>
+          <t>2026-09-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-17 14:30:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-17 14:45:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G36">
@@ -6173,68 +6173,68 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N36">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00:00</t>
+          <t>2026-09-17 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-17 15:45:00</t>
+          <t>2026-09-17 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-17 19:30:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-17 21:00:00</t>
+          <t>2026-09-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-17 21:00:00</t>
+          <t>2026-09-17 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,156 +8086,482 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Kustošija</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Croatia Zmijavci</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Mladost Ždralovi</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Segesta Sisak</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <v>0</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
-      <c r="AD48">
-        <v>0</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>0</v>
-      </c>
-      <c r="AG48">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G20">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G33">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU50"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G33">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G45">
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G49">
@@ -8399,169 +8399,6 @@
         <v>0</v>
       </c>
       <c r="AU49" t="inlineStr">
-        <is>
-          <t>2026-09-17 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Gualberto Villarroel SJ</t>
-        </is>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <v>0</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>0</v>
-      </c>
-      <c r="AB50">
-        <v>0</v>
-      </c>
-      <c r="AC50">
-        <v>0</v>
-      </c>
-      <c r="AD50">
-        <v>0</v>
-      </c>
-      <c r="AE50">
-        <v>0</v>
-      </c>
-      <c r="AF50">
-        <v>0</v>
-      </c>
-      <c r="AG50">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>0</v>
-      </c>
-      <c r="AK50">
-        <v>0</v>
-      </c>
-      <c r="AL50">
-        <v>0</v>
-      </c>
-      <c r="AM50">
-        <v>-1</v>
-      </c>
-      <c r="AN50">
-        <v>-1</v>
-      </c>
-      <c r="AO50">
-        <v>-1</v>
-      </c>
-      <c r="AP50">
-        <v>-1</v>
-      </c>
-      <c r="AQ50">
-        <v>0</v>
-      </c>
-      <c r="AR50">
-        <v>0</v>
-      </c>
-      <c r="AS50">
-        <v>0</v>
-      </c>
-      <c r="AT50">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G30">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G2">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-09-17 10:15:00</t>
+          <t>2026-09-17 10:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:00:00</t>
+          <t>2026-09-17 10:15:00</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G5">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G6">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-09-17 12:00:00</t>
+          <t>2026-09-17 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,68 +1609,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G9">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-09-17 12:30:00</t>
+          <t>2026-09-17 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-09-17 13:00:00</t>
+          <t>2026-09-17 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Leningradets</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Leningradets</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-17 13:30:00</t>
+          <t>2026-09-17 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-17 14:00:00</t>
+          <t>2026-09-17 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-17 14:30:00</t>
+          <t>2026-09-17 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-17 14:45:00</t>
+          <t>2026-09-17 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-17 15:00:00</t>
+          <t>2026-09-17 14:45:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,68 +6662,68 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-17 15:45:00</t>
+          <t>2026-09-17 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-17 16:00:00</t>
+          <t>2026-09-17 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:00</t>
+          <t>2026-09-17 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,27 +7923,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-17 19:30:00</t>
+          <t>2026-09-17 16:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-17 21:00:00</t>
+          <t>2026-09-17 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8249,156 +8249,319 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Croatia Druga HNL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kustošija</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Croatia Zmijavci</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-09-17 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Bolívar</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
-      <c r="T49">
-        <v>0</v>
-      </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
-      <c r="V49">
-        <v>0</v>
-      </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
-      <c r="Z49">
-        <v>0</v>
-      </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
-      <c r="AB49">
-        <v>0</v>
-      </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>0</v>
-      </c>
-      <c r="AK49">
-        <v>0</v>
-      </c>
-      <c r="AL49">
-        <v>0</v>
-      </c>
-      <c r="AM49">
-        <v>-1</v>
-      </c>
-      <c r="AN49">
-        <v>-1</v>
-      </c>
-      <c r="AO49">
-        <v>-1</v>
-      </c>
-      <c r="AP49">
-        <v>-1</v>
-      </c>
-      <c r="AQ49">
-        <v>0</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>0</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>0</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>0</v>
+      </c>
+      <c r="AE50">
+        <v>0</v>
+      </c>
+      <c r="AF50">
+        <v>0</v>
+      </c>
+      <c r="AG50">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>0</v>
+      </c>
+      <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>-1</v>
+      </c>
+      <c r="AN50">
+        <v>-1</v>
+      </c>
+      <c r="AO50">
+        <v>-1</v>
+      </c>
+      <c r="AP50">
+        <v>-1</v>
+      </c>
+      <c r="AQ50">
+        <v>0</v>
+      </c>
+      <c r="AR50">
+        <v>0</v>
+      </c>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+      <c r="AT50">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>2026-09-17 21:30:00</t>
         </is>

--- a/jogos_2026-09-17.xlsx
+++ b/jogos_2026-09-17.xlsx
@@ -8086,7 +8086,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-17 19:30:00</t>
+          <t>2026-09-17 19:00:00</t>
         </is>
       </c>
     </row>
